--- a/leave_request_forms/028_international_training_leave_of_absence_request--leave_request_forms.xlsx
+++ b/leave_request_forms/028_international_training_leave_of_absence_request--leave_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1336,12 +1336,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1404,12 +1404,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1421,12 +1421,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1438,12 +1438,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1455,12 +1455,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1472,12 +1472,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1506,12 +1506,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1523,12 +1523,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1540,12 +1540,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1591,12 +1591,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1608,12 +1608,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1659,12 +1659,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1676,12 +1676,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1693,12 +1693,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1710,12 +1710,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1727,12 +1727,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
